--- a/back/storage/app/ads/2026-08/Davina-report-Agustus.xlsx
+++ b/back/storage/app/ads/2026-08/Davina-report-Agustus.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="38">
   <si>
     <t>Campaign name</t>
   </si>
@@ -20,6 +20,9 @@
     <t>Day</t>
   </si>
   <si>
+    <t>Ad set name</t>
+  </si>
+  <si>
     <t>Delivery status</t>
   </si>
   <si>
@@ -68,16 +71,31 @@
     <t>2026-08-12</t>
   </si>
   <si>
+    <t>PULSE-NEW-AUG2-gym</t>
+  </si>
+  <si>
     <t>active</t>
   </si>
   <si>
-    <t>campaign</t>
+    <t>adset</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>PULSE-NEW-AUG1-resto</t>
+  </si>
+  <si>
+    <t>PULSE BDAY</t>
   </si>
   <si>
     <t>Messaging conversations started</t>
   </si>
   <si>
-    <t/>
+    <t>Kembali-Adset-2-Coffee-Agustus</t>
+  </si>
+  <si>
+    <t>Ladies-Adset-1-july</t>
   </si>
   <si>
     <t>2026-08-11</t>
@@ -475,10 +493,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="17" max="16384" style="1" width="12.7109375"/>
+    <col min="18" max="16384" style="1" width="12.7109375"/>
+    <col min="17" max="17" style="1" width="23.4375" customWidth="true"/>
     <col min="16" max="16" style="1" width="23.4375" customWidth="true"/>
     <col min="15" max="15" style="1" width="23.4375" customWidth="true"/>
     <col min="14" max="14" style="1" width="23.4375" customWidth="true"/>
@@ -546,555 +565,1969 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="C2" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="D2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>1456.0</v>
+        <v>20</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>2043.0</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>1.40315934</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>68147.0</v>
+        <v>499.0</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>679.0</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>1.36072144</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>68147.0</v>
-      </c>
-      <c r="L2" s="6" t="n">
-        <v>2062.0</v>
+        <v>39445.0</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M2" s="6" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>17</v>
+        <v>701.0</v>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>14.0</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="C3" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="D3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>1021.0</v>
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1416.0</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>1.38687561</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="6" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1.42553191</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>2791.0</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="N3" s="6" t="n">
         <v>3.0</v>
       </c>
-      <c r="J3" s="8" t="n">
-        <v>80446.0</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>26815.33333333</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>1421.0</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>22</v>
-      </c>
       <c r="O3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="C4" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="D4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>2890.0</v>
+        <v>20</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>3649.0</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1.26262976</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>56146.0</v>
+        <v>747.0</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>944.0</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.26372155</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.0</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>28073.0</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>3664.0</v>
+        <v>14374.0</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>14374.0</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>23</v>
+        <v>944.0</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>10.0</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="C5" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="D5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>2213.0</v>
+        <v>20</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2995.0</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1.35336647</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="6" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1.63265306</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>4245.0</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="N5" s="6" t="n">
         <v>2.0</v>
       </c>
-      <c r="J5" s="8" t="n">
-        <v>56145.0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>28072.5</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>3014.0</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>24</v>
-      </c>
       <c r="O5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="C6" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="D6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>2129.0</v>
+        <v>20</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2773.0</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1.30248943</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>62243.0</v>
+        <v>239.0</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>273.0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.14225941</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>62243.0</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>2777.0</v>
+        <v>7292.0</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>25</v>
+        <v>271.0</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>3.0</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1962.0</v>
+        <v>20</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2653.0</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1.35219164</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>79794.0</v>
+        <v>546.0</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>655.0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.1996337</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>26598.0</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>2692.0</v>
+        <v>11418.0</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>26</v>
+        <v>651.0</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>2.0</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>1565.0</v>
+        <v>20</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>2168.0</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>1.38530351</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>87810.0</v>
+        <v>135.0</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>157.0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1.16296296</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>87810.0</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>2200.0</v>
+        <v>7527.0</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>27</v>
+        <v>163.0</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>3.0</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>18</v>
+      <c r="C9" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>2.0</v>
+        <v>20</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G9" s="6" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>89.0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.32835821</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>1.0</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="8" t="n">
+      <c r="K9" s="8" t="n">
+        <v>6888.0</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>6888.0</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="N9" s="6" t="n">
         <v>1.0</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>28</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>21</v>
+      <c r="P9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1464.0</v>
+        <v>20</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1784.0</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1.21857923</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>59849.0</v>
+        <v>25.0</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.0</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>8549.85714286</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>1807.0</v>
+        <v>4492.0</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>4492.0</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>29</v>
+        <v>45.0</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>5.0</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>6935.0</v>
+        <v>20</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>8183.0</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>1.17995674</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="6" t="n">
+        <v>313.0</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>468.0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1.49520767</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="6" t="n">
         <v>1.0</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>120330.0</v>
-      </c>
       <c r="K11" s="8" t="n">
-        <v>120330.0</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>8105.0</v>
+        <v>50121.0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>50121.0</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>30</v>
+        <v>477.0</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>18.0</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>175.0</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>208.0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.18857143</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>8977.0</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>8977.0</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>203.0</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.33333333</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>750.0</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>2490.0</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>3072.0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1.23373494</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>34416.0</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>3106.0</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.73469388</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>3629.0</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>237.0</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>268.0</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1.13080169</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>8374.0</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>8374.0</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>264.0</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>218.0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>255.0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1.16972477</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>7918.0</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>7918.0</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>261.0</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>2022.0</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>2708.0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.33926805</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>47339.0</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>47339.0</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>2724.0</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1.52380952</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>888.0</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>3352.0</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>4323.0</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1.2896778</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="6" t="n">
+      <c r="C20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1929.0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>2507.0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1.29963712</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>51012.0</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>51012.0</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>2519.0</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>213.0</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>236.0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.10798122</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>9840.0</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>228.0</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1.76470588</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>1391.0</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>1808.0</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>2425.0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1.34126106</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>2.0</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>92992.0</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>46496.0</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>4429.0</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>21</v>
+      <c r="K23" s="8" t="n">
+        <v>66462.0</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>33231.0</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>2461.0</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q23" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>3127.0</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>165.0</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1.05769231</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>10205.0</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>10205.0</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>167.0</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q25" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1404.0</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1897.0</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1.3511396</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>76444.0</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>76444.0</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>1933.0</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>143.0</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>8453.0</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>136.0</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>2913.0</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>131.0</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>257.0</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>277.0</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>1.07782101</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>9600.0</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>4800.0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>263.0</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>1.13636364</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>2245.0</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q31" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1251.0</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>1482.0</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1.18465228</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>48004.0</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>9600.8</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>1520.0</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P32" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q32" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>4316.0</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>4801.0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1.11237257</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>93327.0</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>4792.0</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>2835.0</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>3275.0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>1.15520282</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="8" t="n">
+        <v>23244.0</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>3202.0</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>107.0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>1.12631579</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>3759.0</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>3759.0</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>111.0</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>190.0</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>253.0</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>1.33157895</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="8" t="n">
+        <v>12620.0</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>256.0</v>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P36" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>2289.0</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>2765.0</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>1.20795107</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>38856.0</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>19428.0</v>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>2847.0</v>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P37" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q37" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1051.0</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>1305.0</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1.2416746</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="8" t="n">
+        <v>41516.0</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>1326.0</v>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P38" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/back/storage/app/ads/2026-08/Davina-report-Agustus.xlsx
+++ b/back/storage/app/ads/2026-08/Davina-report-Agustus.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-08\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E44109-0701-4DFF-AC0E-3BD338C91007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw Data Report" r:id="rId3" sheetId="1"/>
+    <sheet name="Raw Data Report" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="38">
   <si>
     <t>Campaign name</t>
   </si>
@@ -131,57 +139,44 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <b val="true"/>
-      <u val="none"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="FFFFFF"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -192,249 +187,37 @@
     <border>
       <left/>
       <right/>
-      <top>
-        <color rgb="000000"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
+      <left style="thin">
+        <color rgb="FF90949C"/>
       </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
+      <right style="thin">
+        <color rgb="FF90949C"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF90949C"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF90949C"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="90949C"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -443,80 +226,357 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q38"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="18" max="16384" style="1" width="12.7109375"/>
-    <col min="17" max="17" style="1" width="23.4375" customWidth="true"/>
-    <col min="16" max="16" style="1" width="23.4375" customWidth="true"/>
-    <col min="15" max="15" style="1" width="23.4375" customWidth="true"/>
-    <col min="14" max="14" style="1" width="23.4375" customWidth="true"/>
-    <col min="13" max="13" style="1" width="23.4375" customWidth="true"/>
-    <col min="12" max="12" style="1" width="23.4375" customWidth="true"/>
-    <col min="11" max="11" style="1" width="23.4375" customWidth="true"/>
-    <col min="10" max="10" style="1" width="23.4375" customWidth="true"/>
-    <col min="9" max="9" style="1" width="23.4375" customWidth="true"/>
-    <col min="8" max="8" style="1" width="23.4375" customWidth="true"/>
-    <col min="7" max="7" style="1" width="23.4375" customWidth="true"/>
-    <col min="6" max="6" style="1" width="23.4375" customWidth="true"/>
-    <col min="5" max="5" style="1" width="23.4375" customWidth="true"/>
-    <col min="4" max="4" style="1" width="23.4375" customWidth="true"/>
-    <col min="3" max="3" style="1" width="23.4375" customWidth="true"/>
-    <col min="2" max="2" style="1" width="23.4375" customWidth="true"/>
-    <col min="1" max="1" width="58.59375" style="1" customWidth="true"/>
+    <col min="1" max="1" width="58.6328125" style="1" customWidth="1"/>
+    <col min="2" max="17" width="23.453125" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="12.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -569,7 +629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -585,14 +645,14 @@
       <c r="E2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>499.0</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>679.0</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>1.36072144</v>
+      <c r="F2" s="7">
+        <v>499</v>
+      </c>
+      <c r="G2" s="7">
+        <v>679</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1.3607214400000001</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>22</v>
@@ -600,17 +660,17 @@
       <c r="J2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="8" t="n">
-        <v>39445.0</v>
+      <c r="K2" s="8">
+        <v>39445</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="6" t="n">
-        <v>701.0</v>
-      </c>
-      <c r="N2" s="6" t="n">
-        <v>14.0</v>
+      <c r="M2" s="6">
+        <v>701</v>
+      </c>
+      <c r="N2" s="6">
+        <v>14</v>
       </c>
       <c r="O2" s="9" t="s">
         <v>18</v>
@@ -622,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -638,14 +698,14 @@
       <c r="E3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>67.0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>1.42553191</v>
+      <c r="F3" s="7">
+        <v>47</v>
+      </c>
+      <c r="G3" s="7">
+        <v>67</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1.4255319099999999</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>22</v>
@@ -653,17 +713,17 @@
       <c r="J3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="8" t="n">
-        <v>2791.0</v>
+      <c r="K3" s="8">
+        <v>2791</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="6" t="n">
-        <v>67.0</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>3.0</v>
+      <c r="M3" s="6">
+        <v>67</v>
+      </c>
+      <c r="N3" s="6">
+        <v>3</v>
       </c>
       <c r="O3" s="9" t="s">
         <v>18</v>
@@ -675,7 +735,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -691,32 +751,32 @@
       <c r="E4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="7" t="n">
-        <v>747.0</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>944.0</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1.26372155</v>
+      <c r="F4" s="7">
+        <v>747</v>
+      </c>
+      <c r="G4" s="7">
+        <v>944</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1.2637215500000001</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>14374.0</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>14374.0</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>944.0</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>10.0</v>
+      <c r="J4" s="6">
+        <v>1</v>
+      </c>
+      <c r="K4" s="8">
+        <v>14374</v>
+      </c>
+      <c r="L4" s="8">
+        <v>14374</v>
+      </c>
+      <c r="M4" s="6">
+        <v>944</v>
+      </c>
+      <c r="N4" s="6">
+        <v>10</v>
       </c>
       <c r="O4" s="9" t="s">
         <v>18</v>
@@ -728,7 +788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -744,13 +804,13 @@
       <c r="E5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="7" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="F5" s="7">
+        <v>49</v>
+      </c>
+      <c r="G5" s="7">
+        <v>80</v>
+      </c>
+      <c r="H5" s="6">
         <v>1.63265306</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -759,17 +819,17 @@
       <c r="J5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="8" t="n">
-        <v>4245.0</v>
+      <c r="K5" s="8">
+        <v>4245</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="6" t="n">
-        <v>79.0</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>2.0</v>
+      <c r="M5" s="6">
+        <v>79</v>
+      </c>
+      <c r="N5" s="6">
+        <v>2</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>18</v>
@@ -781,7 +841,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -797,14 +857,14 @@
       <c r="E6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="7" t="n">
-        <v>239.0</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>273.0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>1.14225941</v>
+      <c r="F6" s="7">
+        <v>239</v>
+      </c>
+      <c r="G6" s="7">
+        <v>273</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1.1422594100000001</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>22</v>
@@ -812,17 +872,17 @@
       <c r="J6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="8" t="n">
-        <v>7292.0</v>
+      <c r="K6" s="8">
+        <v>7292</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="6" t="n">
-        <v>271.0</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>3.0</v>
+      <c r="M6" s="6">
+        <v>271</v>
+      </c>
+      <c r="N6" s="6">
+        <v>3</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>18</v>
@@ -834,7 +894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -850,14 +910,14 @@
       <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>546.0</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>655.0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1.1996337</v>
+      <c r="F7" s="7">
+        <v>546</v>
+      </c>
+      <c r="G7" s="7">
+        <v>655</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.1996336999999999</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>22</v>
@@ -865,17 +925,17 @@
       <c r="J7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>11418.0</v>
+      <c r="K7" s="8">
+        <v>11418</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="6" t="n">
-        <v>651.0</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>2.0</v>
+      <c r="M7" s="6">
+        <v>651</v>
+      </c>
+      <c r="N7" s="6">
+        <v>2</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>28</v>
@@ -887,7 +947,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -903,13 +963,13 @@
       <c r="E8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>135.0</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>157.0</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="F8" s="7">
+        <v>135</v>
+      </c>
+      <c r="G8" s="7">
+        <v>157</v>
+      </c>
+      <c r="H8" s="6">
         <v>1.16296296</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -918,17 +978,17 @@
       <c r="J8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>7527.0</v>
+      <c r="K8" s="8">
+        <v>7527</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="6" t="n">
-        <v>163.0</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>3.0</v>
+      <c r="M8" s="6">
+        <v>163</v>
+      </c>
+      <c r="N8" s="6">
+        <v>3</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>28</v>
@@ -940,7 +1000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -956,32 +1016,32 @@
       <c r="E9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>67.0</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>89.0</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="F9" s="7">
+        <v>67</v>
+      </c>
+      <c r="G9" s="7">
+        <v>89</v>
+      </c>
+      <c r="H9" s="6">
         <v>1.32835821</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>6888.0</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>6888.0</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>1.0</v>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8">
+        <v>6888</v>
+      </c>
+      <c r="L9" s="8">
+        <v>6888</v>
+      </c>
+      <c r="M9" s="6">
+        <v>85</v>
+      </c>
+      <c r="N9" s="6">
+        <v>1</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>28</v>
@@ -993,7 +1053,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -1009,32 +1069,32 @@
       <c r="E10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="F10" s="7">
+        <v>25</v>
+      </c>
+      <c r="G10" s="7">
+        <v>47</v>
+      </c>
+      <c r="H10" s="6">
         <v>1.88</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>4492.0</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>4492.0</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>5.0</v>
+      <c r="J10" s="6">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8">
+        <v>4492</v>
+      </c>
+      <c r="L10" s="8">
+        <v>4492</v>
+      </c>
+      <c r="M10" s="6">
+        <v>45</v>
+      </c>
+      <c r="N10" s="6">
+        <v>5</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>28</v>
@@ -1046,7 +1106,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1062,32 +1122,32 @@
       <c r="E11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>313.0</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>468.0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1.49520767</v>
+      <c r="F11" s="7">
+        <v>313</v>
+      </c>
+      <c r="G11" s="7">
+        <v>468</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1.4952076700000001</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>50121.0</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>50121.0</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>477.0</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>18.0</v>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
+        <v>50121</v>
+      </c>
+      <c r="L11" s="8">
+        <v>50121</v>
+      </c>
+      <c r="M11" s="6">
+        <v>477</v>
+      </c>
+      <c r="N11" s="6">
+        <v>18</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>28</v>
@@ -1099,7 +1159,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
@@ -1115,32 +1175,32 @@
       <c r="E12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>175.0</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>208.0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1.18857143</v>
+      <c r="F12" s="7">
+        <v>175</v>
+      </c>
+      <c r="G12" s="7">
+        <v>208</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1.1885714300000001</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J12" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>8977.0</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>8977.0</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>203.0</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>5.0</v>
+      <c r="J12" s="6">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8">
+        <v>8977</v>
+      </c>
+      <c r="L12" s="8">
+        <v>8977</v>
+      </c>
+      <c r="M12" s="6">
+        <v>203</v>
+      </c>
+      <c r="N12" s="6">
+        <v>5</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>29</v>
@@ -1152,7 +1212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -1168,14 +1228,14 @@
       <c r="E13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="7" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>1.33333333</v>
+      <c r="F13" s="7">
+        <v>12</v>
+      </c>
+      <c r="G13" s="7">
+        <v>16</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1.3333333300000001</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>22</v>
@@ -1183,17 +1243,17 @@
       <c r="J13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="8" t="n">
-        <v>750.0</v>
+      <c r="K13" s="8">
+        <v>750</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M13" s="6" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.0</v>
+      <c r="M13" s="6">
+        <v>14</v>
+      </c>
+      <c r="N13" s="6">
+        <v>0</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>29</v>
@@ -1205,7 +1265,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1221,14 +1281,14 @@
       <c r="E14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>2490.0</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>3072.0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>1.23373494</v>
+      <c r="F14" s="7">
+        <v>2490</v>
+      </c>
+      <c r="G14" s="7">
+        <v>3072</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1.2337349399999999</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>22</v>
@@ -1236,17 +1296,17 @@
       <c r="J14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>34416.0</v>
+      <c r="K14" s="8">
+        <v>34416</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M14" s="6" t="n">
-        <v>3106.0</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>22.0</v>
+      <c r="M14" s="6">
+        <v>3106</v>
+      </c>
+      <c r="N14" s="6">
+        <v>22</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>29</v>
@@ -1258,7 +1318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1274,13 +1334,13 @@
       <c r="E15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="H15" s="6" t="n">
+      <c r="F15" s="7">
+        <v>49</v>
+      </c>
+      <c r="G15" s="7">
+        <v>85</v>
+      </c>
+      <c r="H15" s="6">
         <v>1.73469388</v>
       </c>
       <c r="I15" s="6" t="s">
@@ -1289,17 +1349,17 @@
       <c r="J15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="8" t="n">
-        <v>3629.0</v>
+      <c r="K15" s="8">
+        <v>3629</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="6" t="n">
-        <v>77.0</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0.0</v>
+      <c r="M15" s="6">
+        <v>77</v>
+      </c>
+      <c r="N15" s="6">
+        <v>0</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>29</v>
@@ -1311,7 +1371,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
@@ -1327,32 +1387,32 @@
       <c r="E16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="7" t="n">
-        <v>237.0</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>268.0</v>
-      </c>
-      <c r="H16" s="6" t="n">
+      <c r="F16" s="7">
+        <v>237</v>
+      </c>
+      <c r="G16" s="7">
+        <v>268</v>
+      </c>
+      <c r="H16" s="6">
         <v>1.13080169</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J16" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>8374.0</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>8374.0</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>264.0</v>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>4.0</v>
+      <c r="J16" s="6">
+        <v>1</v>
+      </c>
+      <c r="K16" s="8">
+        <v>8374</v>
+      </c>
+      <c r="L16" s="8">
+        <v>8374</v>
+      </c>
+      <c r="M16" s="6">
+        <v>264</v>
+      </c>
+      <c r="N16" s="6">
+        <v>4</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>29</v>
@@ -1364,7 +1424,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
@@ -1380,32 +1440,32 @@
       <c r="E17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="7" t="n">
-        <v>218.0</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="H17" s="6" t="n">
+      <c r="F17" s="7">
+        <v>218</v>
+      </c>
+      <c r="G17" s="7">
+        <v>255</v>
+      </c>
+      <c r="H17" s="6">
         <v>1.16972477</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J17" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>7918.0</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>7918.0</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>261.0</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>16.0</v>
+      <c r="J17" s="6">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8">
+        <v>7918</v>
+      </c>
+      <c r="L17" s="8">
+        <v>7918</v>
+      </c>
+      <c r="M17" s="6">
+        <v>261</v>
+      </c>
+      <c r="N17" s="6">
+        <v>16</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>30</v>
@@ -1417,7 +1477,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -1433,32 +1493,32 @@
       <c r="E18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="7" t="n">
-        <v>2022.0</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>2708.0</v>
-      </c>
-      <c r="H18" s="6" t="n">
+      <c r="F18" s="7">
+        <v>2022</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2708</v>
+      </c>
+      <c r="H18" s="6">
         <v>1.33926805</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>47339.0</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>47339.0</v>
-      </c>
-      <c r="M18" s="6" t="n">
-        <v>2724.0</v>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>25.0</v>
+      <c r="J18" s="6">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8">
+        <v>47339</v>
+      </c>
+      <c r="L18" s="8">
+        <v>47339</v>
+      </c>
+      <c r="M18" s="6">
+        <v>2724</v>
+      </c>
+      <c r="N18" s="6">
+        <v>25</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>30</v>
@@ -1470,7 +1530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
@@ -1486,14 +1546,14 @@
       <c r="E19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="7" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>1.52380952</v>
+      <c r="F19" s="7">
+        <v>21</v>
+      </c>
+      <c r="G19" s="7">
+        <v>32</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1.5238095199999999</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>22</v>
@@ -1501,17 +1561,17 @@
       <c r="J19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="8" t="n">
-        <v>888.0</v>
+      <c r="K19" s="8">
+        <v>888</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M19" s="6" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0.0</v>
+      <c r="M19" s="6">
+        <v>29</v>
+      </c>
+      <c r="N19" s="6">
+        <v>0</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>30</v>
@@ -1523,7 +1583,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
@@ -1539,32 +1599,32 @@
       <c r="E20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="7" t="n">
-        <v>1929.0</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>2507.0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1.29963712</v>
+      <c r="F20" s="7">
+        <v>1929</v>
+      </c>
+      <c r="G20" s="7">
+        <v>2507</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1.2996371200000001</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J20" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>51012.0</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>51012.0</v>
-      </c>
-      <c r="M20" s="6" t="n">
-        <v>2519.0</v>
-      </c>
-      <c r="N20" s="6" t="n">
-        <v>20.0</v>
+      <c r="J20" s="6">
+        <v>1</v>
+      </c>
+      <c r="K20" s="8">
+        <v>784000</v>
+      </c>
+      <c r="L20" s="8">
+        <v>784000</v>
+      </c>
+      <c r="M20" s="6">
+        <v>2519</v>
+      </c>
+      <c r="N20" s="6">
+        <v>20</v>
       </c>
       <c r="O20" s="9" t="s">
         <v>31</v>
@@ -1576,7 +1636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>17</v>
       </c>
@@ -1592,14 +1652,14 @@
       <c r="E21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>213.0</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>236.0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1.10798122</v>
+      <c r="F21" s="7">
+        <v>213</v>
+      </c>
+      <c r="G21" s="7">
+        <v>236</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1.1079812200000001</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>22</v>
@@ -1607,17 +1667,17 @@
       <c r="J21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="8" t="n">
-        <v>9840.0</v>
+      <c r="K21" s="8">
+        <v>9840</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="6" t="n">
-        <v>228.0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>3.0</v>
+      <c r="M21" s="6">
+        <v>228</v>
+      </c>
+      <c r="N21" s="6">
+        <v>3</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>31</v>
@@ -1629,7 +1689,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -1645,14 +1705,14 @@
       <c r="E22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="7" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1.76470588</v>
+      <c r="F22" s="7">
+        <v>17</v>
+      </c>
+      <c r="G22" s="7">
+        <v>30</v>
+      </c>
+      <c r="H22" s="6">
+        <v>1.7647058799999999</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>22</v>
@@ -1660,17 +1720,17 @@
       <c r="J22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K22" s="8" t="n">
-        <v>1391.0</v>
+      <c r="K22" s="8">
+        <v>1391</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M22" s="6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="N22" s="6" t="n">
-        <v>1.0</v>
+      <c r="M22" s="6">
+        <v>30</v>
+      </c>
+      <c r="N22" s="6">
+        <v>1</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>31</v>
@@ -1682,7 +1742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
@@ -1698,32 +1758,32 @@
       <c r="E23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="7" t="n">
-        <v>1808.0</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>2425.0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1.34126106</v>
+      <c r="F23" s="7">
+        <v>1808</v>
+      </c>
+      <c r="G23" s="7">
+        <v>2425</v>
+      </c>
+      <c r="H23" s="6">
+        <v>1.3412610599999999</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K23" s="8" t="n">
-        <v>66462.0</v>
-      </c>
-      <c r="L23" s="8" t="n">
-        <v>33231.0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>2461.0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>40.0</v>
+      <c r="J23" s="6">
+        <v>2</v>
+      </c>
+      <c r="K23" s="8">
+        <v>66462</v>
+      </c>
+      <c r="L23" s="8">
+        <v>33231</v>
+      </c>
+      <c r="M23" s="6">
+        <v>2461</v>
+      </c>
+      <c r="N23" s="6">
+        <v>40</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>32</v>
@@ -1735,7 +1795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>17</v>
       </c>
@@ -1751,13 +1811,13 @@
       <c r="E24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="7" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>63.0</v>
-      </c>
-      <c r="H24" s="6" t="n">
+      <c r="F24" s="7">
+        <v>35</v>
+      </c>
+      <c r="G24" s="7">
+        <v>63</v>
+      </c>
+      <c r="H24" s="6">
         <v>1.8</v>
       </c>
       <c r="I24" s="6" t="s">
@@ -1766,17 +1826,17 @@
       <c r="J24" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>3127.0</v>
+      <c r="K24" s="8">
+        <v>3127</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M24" s="6" t="n">
-        <v>64.0</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>2.0</v>
+      <c r="M24" s="6">
+        <v>64</v>
+      </c>
+      <c r="N24" s="6">
+        <v>2</v>
       </c>
       <c r="O24" s="9" t="s">
         <v>32</v>
@@ -1788,7 +1848,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>17</v>
       </c>
@@ -1804,32 +1864,32 @@
       <c r="E25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>156.0</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>165.0</v>
-      </c>
-      <c r="H25" s="6" t="n">
+      <c r="F25" s="7">
+        <v>156</v>
+      </c>
+      <c r="G25" s="7">
+        <v>165</v>
+      </c>
+      <c r="H25" s="6">
         <v>1.05769231</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J25" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>10205.0</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>10205.0</v>
-      </c>
-      <c r="M25" s="6" t="n">
-        <v>167.0</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>3.0</v>
+      <c r="J25" s="6">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8">
+        <v>10205</v>
+      </c>
+      <c r="L25" s="8">
+        <v>10205</v>
+      </c>
+      <c r="M25" s="6">
+        <v>167</v>
+      </c>
+      <c r="N25" s="6">
+        <v>3</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>32</v>
@@ -1841,7 +1901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>17</v>
       </c>
@@ -1857,32 +1917,32 @@
       <c r="E26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>1404.0</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>1897.0</v>
-      </c>
-      <c r="H26" s="6" t="n">
+      <c r="F26" s="7">
+        <v>12900</v>
+      </c>
+      <c r="G26" s="7">
+        <v>1897</v>
+      </c>
+      <c r="H26" s="6">
         <v>1.3511396</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J26" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K26" s="8" t="n">
-        <v>76444.0</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>76444.0</v>
-      </c>
-      <c r="M26" s="6" t="n">
-        <v>1933.0</v>
-      </c>
-      <c r="N26" s="6" t="n">
-        <v>23.0</v>
+      <c r="J26" s="6">
+        <v>1</v>
+      </c>
+      <c r="K26" s="8">
+        <v>2754000</v>
+      </c>
+      <c r="L26" s="8">
+        <v>2754000</v>
+      </c>
+      <c r="M26" s="6">
+        <v>1933</v>
+      </c>
+      <c r="N26" s="6">
+        <v>23</v>
       </c>
       <c r="O26" s="9" t="s">
         <v>33</v>
@@ -1894,7 +1954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>17</v>
       </c>
@@ -1910,13 +1970,13 @@
       <c r="E27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="7" t="n">
-        <v>88.0</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>143.0</v>
-      </c>
-      <c r="H27" s="6" t="n">
+      <c r="F27" s="7">
+        <v>88</v>
+      </c>
+      <c r="G27" s="7">
+        <v>143</v>
+      </c>
+      <c r="H27" s="6">
         <v>1.625</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -1925,17 +1985,17 @@
       <c r="J27" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="8" t="n">
-        <v>8453.0</v>
+      <c r="K27" s="8">
+        <v>8453</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M27" s="6" t="n">
-        <v>136.0</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0.0</v>
+      <c r="M27" s="6">
+        <v>136</v>
+      </c>
+      <c r="N27" s="6">
+        <v>0</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>33</v>
@@ -1947,7 +2007,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
@@ -1963,13 +2023,13 @@
       <c r="E28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="7" t="n">
-        <v>125.0</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>128.0</v>
-      </c>
-      <c r="H28" s="6" t="n">
+      <c r="F28" s="7">
+        <v>125</v>
+      </c>
+      <c r="G28" s="7">
+        <v>128</v>
+      </c>
+      <c r="H28" s="6">
         <v>1.024</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -1978,17 +2038,17 @@
       <c r="J28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K28" s="8" t="n">
-        <v>2913.0</v>
+      <c r="K28" s="8">
+        <v>2913</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M28" s="6" t="n">
-        <v>131.0</v>
-      </c>
-      <c r="N28" s="6" t="n">
-        <v>2.0</v>
+      <c r="M28" s="6">
+        <v>131</v>
+      </c>
+      <c r="N28" s="6">
+        <v>2</v>
       </c>
       <c r="O28" s="9" t="s">
         <v>33</v>
@@ -2000,7 +2060,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>17</v>
       </c>
@@ -2016,14 +2076,14 @@
       <c r="E29" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>1.0</v>
+      <c r="F29" s="7">
+        <v>2</v>
+      </c>
+      <c r="G29" s="7">
+        <v>2</v>
+      </c>
+      <c r="H29" s="6">
+        <v>1</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>22</v>
@@ -2031,17 +2091,17 @@
       <c r="J29" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K29" s="8" t="n">
-        <v>1.0</v>
+      <c r="K29" s="8">
+        <v>1</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M29" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>0.0</v>
+      <c r="M29" s="6">
+        <v>1</v>
+      </c>
+      <c r="N29" s="6">
+        <v>0</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>34</v>
@@ -2053,7 +2113,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>17</v>
       </c>
@@ -2069,32 +2129,32 @@
       <c r="E30" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="7" t="n">
-        <v>257.0</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>277.0</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>1.07782101</v>
+      <c r="F30" s="7">
+        <v>257</v>
+      </c>
+      <c r="G30" s="7">
+        <v>277</v>
+      </c>
+      <c r="H30" s="6">
+        <v>1.0778210100000001</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J30" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K30" s="8" t="n">
-        <v>9600.0</v>
-      </c>
-      <c r="L30" s="8" t="n">
-        <v>4800.0</v>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>263.0</v>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>3.0</v>
+      <c r="J30" s="6">
+        <v>2</v>
+      </c>
+      <c r="K30" s="8">
+        <v>9600</v>
+      </c>
+      <c r="L30" s="8">
+        <v>4800</v>
+      </c>
+      <c r="M30" s="6">
+        <v>263</v>
+      </c>
+      <c r="N30" s="6">
+        <v>3</v>
       </c>
       <c r="O30" s="9" t="s">
         <v>35</v>
@@ -2106,7 +2166,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>17</v>
       </c>
@@ -2122,14 +2182,14 @@
       <c r="E31" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="7" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>1.13636364</v>
+      <c r="F31" s="7">
+        <v>22</v>
+      </c>
+      <c r="G31" s="7">
+        <v>25</v>
+      </c>
+      <c r="H31" s="6">
+        <v>1.1363636399999999</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>22</v>
@@ -2137,17 +2197,17 @@
       <c r="J31" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="8" t="n">
-        <v>2245.0</v>
+      <c r="K31" s="8">
+        <v>2245</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M31" s="6" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>1.0</v>
+      <c r="M31" s="6">
+        <v>24</v>
+      </c>
+      <c r="N31" s="6">
+        <v>1</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>35</v>
@@ -2159,7 +2219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>17</v>
       </c>
@@ -2175,32 +2235,32 @@
       <c r="E32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F32" s="7" t="n">
-        <v>1251.0</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>1482.0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1.18465228</v>
+      <c r="F32" s="7">
+        <v>1251</v>
+      </c>
+      <c r="G32" s="7">
+        <v>1482</v>
+      </c>
+      <c r="H32" s="6">
+        <v>1.1846522799999999</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J32" s="6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="K32" s="8" t="n">
-        <v>48004.0</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>9600.8</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>1520.0</v>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>32.0</v>
+      <c r="J32" s="6">
+        <v>5</v>
+      </c>
+      <c r="K32" s="8">
+        <v>48004</v>
+      </c>
+      <c r="L32" s="8">
+        <v>9600.7999999999993</v>
+      </c>
+      <c r="M32" s="6">
+        <v>1520</v>
+      </c>
+      <c r="N32" s="6">
+        <v>32</v>
       </c>
       <c r="O32" s="9" t="s">
         <v>35</v>
@@ -2212,7 +2272,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>17</v>
       </c>
@@ -2228,13 +2288,13 @@
       <c r="E33" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="7" t="n">
-        <v>4316.0</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>4801.0</v>
-      </c>
-      <c r="H33" s="6" t="n">
+      <c r="F33" s="7">
+        <v>6789</v>
+      </c>
+      <c r="G33" s="7">
+        <v>7866</v>
+      </c>
+      <c r="H33" s="6">
         <v>1.11237257</v>
       </c>
       <c r="I33" s="6" t="s">
@@ -2243,17 +2303,17 @@
       <c r="J33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K33" s="8" t="n">
-        <v>93327.0</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M33" s="6" t="n">
-        <v>4792.0</v>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>20.0</v>
+      <c r="K33" s="8">
+        <v>93327</v>
+      </c>
+      <c r="L33" s="8">
+        <v>3765000</v>
+      </c>
+      <c r="M33" s="6">
+        <v>4792</v>
+      </c>
+      <c r="N33" s="6">
+        <v>20</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>36</v>
@@ -2265,7 +2325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>17</v>
       </c>
@@ -2281,13 +2341,13 @@
       <c r="E34" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F34" s="7" t="n">
-        <v>2835.0</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>3275.0</v>
-      </c>
-      <c r="H34" s="6" t="n">
+      <c r="F34" s="7">
+        <v>2835</v>
+      </c>
+      <c r="G34" s="7">
+        <v>3275</v>
+      </c>
+      <c r="H34" s="6">
         <v>1.15520282</v>
       </c>
       <c r="I34" s="6" t="s">
@@ -2296,17 +2356,17 @@
       <c r="J34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="8" t="n">
-        <v>23244.0</v>
+      <c r="K34" s="8">
+        <v>23244</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M34" s="6" t="n">
-        <v>3202.0</v>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>18.0</v>
+      <c r="M34" s="6">
+        <v>3202</v>
+      </c>
+      <c r="N34" s="6">
+        <v>18</v>
       </c>
       <c r="O34" s="9" t="s">
         <v>36</v>
@@ -2318,7 +2378,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>17</v>
       </c>
@@ -2334,32 +2394,32 @@
       <c r="E35" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F35" s="7" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>107.0</v>
-      </c>
-      <c r="H35" s="6" t="n">
+      <c r="F35" s="7">
+        <v>95</v>
+      </c>
+      <c r="G35" s="7">
+        <v>107</v>
+      </c>
+      <c r="H35" s="6">
         <v>1.12631579</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J35" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K35" s="8" t="n">
-        <v>3759.0</v>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>3759.0</v>
-      </c>
-      <c r="M35" s="6" t="n">
-        <v>111.0</v>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>4.0</v>
+      <c r="J35" s="6">
+        <v>1</v>
+      </c>
+      <c r="K35" s="8">
+        <v>3759</v>
+      </c>
+      <c r="L35" s="8">
+        <v>3759</v>
+      </c>
+      <c r="M35" s="6">
+        <v>111</v>
+      </c>
+      <c r="N35" s="6">
+        <v>4</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>36</v>
@@ -2371,7 +2431,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>17</v>
       </c>
@@ -2387,14 +2447,14 @@
       <c r="E36" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F36" s="7" t="n">
-        <v>190.0</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>253.0</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>1.33157895</v>
+      <c r="F36" s="7">
+        <v>190</v>
+      </c>
+      <c r="G36" s="7">
+        <v>253</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1.3315789499999999</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>22</v>
@@ -2402,17 +2462,17 @@
       <c r="J36" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="8" t="n">
-        <v>12620.0</v>
+      <c r="K36" s="8">
+        <v>12620</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M36" s="6" t="n">
-        <v>256.0</v>
-      </c>
-      <c r="N36" s="6" t="n">
-        <v>3.0</v>
+      <c r="M36" s="6">
+        <v>256</v>
+      </c>
+      <c r="N36" s="6">
+        <v>3</v>
       </c>
       <c r="O36" s="9" t="s">
         <v>37</v>
@@ -2424,7 +2484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>17</v>
       </c>
@@ -2440,32 +2500,32 @@
       <c r="E37" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="7" t="n">
-        <v>2289.0</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>2765.0</v>
-      </c>
-      <c r="H37" s="6" t="n">
+      <c r="F37" s="7">
+        <v>2289</v>
+      </c>
+      <c r="G37" s="7">
+        <v>2765</v>
+      </c>
+      <c r="H37" s="6">
         <v>1.20795107</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J37" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K37" s="8" t="n">
-        <v>38856.0</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>19428.0</v>
-      </c>
-      <c r="M37" s="6" t="n">
-        <v>2847.0</v>
-      </c>
-      <c r="N37" s="6" t="n">
-        <v>16.0</v>
+      <c r="J37" s="6">
+        <v>2</v>
+      </c>
+      <c r="K37" s="8">
+        <v>38856</v>
+      </c>
+      <c r="L37" s="8">
+        <v>19428</v>
+      </c>
+      <c r="M37" s="6">
+        <v>2847</v>
+      </c>
+      <c r="N37" s="6">
+        <v>16</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>37</v>
@@ -2477,7 +2537,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>17</v>
       </c>
@@ -2493,14 +2553,14 @@
       <c r="E38" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F38" s="7" t="n">
-        <v>1051.0</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>1305.0</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>1.2416746</v>
+      <c r="F38" s="7">
+        <v>1051</v>
+      </c>
+      <c r="G38" s="7">
+        <v>1305</v>
+      </c>
+      <c r="H38" s="6">
+        <v>1.2416746000000001</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>22</v>
@@ -2508,17 +2568,17 @@
       <c r="J38" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="8" t="n">
-        <v>41516.0</v>
+      <c r="K38" s="8">
+        <v>41516</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M38" s="6" t="n">
-        <v>1326.0</v>
-      </c>
-      <c r="N38" s="6" t="n">
-        <v>23.0</v>
+      <c r="M38" s="6">
+        <v>1326</v>
+      </c>
+      <c r="N38" s="6">
+        <v>23</v>
       </c>
       <c r="O38" s="9" t="s">
         <v>37</v>
@@ -2531,7 +2591,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>